--- a/public/templates/Feasibility Study_Order_Review_Template.xlsx
+++ b/public/templates/Feasibility Study_Order_Review_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lapto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80B8B4D6-3307-42DA-B48D-085244EAD70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FE22BF4-5EED-4987-BDF8-5FBDE94D5011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -363,7 +363,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,8 +394,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -498,11 +504,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -551,9 +598,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -578,35 +622,42 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -635,23 +686,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1057,34 +1093,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" ht="52.9" customHeight="1">
-      <c r="A1" s="25"/>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="17"/>
+      <c r="A1" s="34"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="33"/>
       <c r="T1" s="17"/>
       <c r="U1" s="17"/>
       <c r="V1" s="17"/>
       <c r="W1" s="17"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="36"/>
-      <c r="Z1" s="37"/>
+      <c r="X1" s="37"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="39"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="9"/>
       <c r="AC1" s="9"/>
@@ -1095,65 +1131,65 @@
       <c r="AH1" s="11"/>
       <c r="AI1" s="11"/>
     </row>
-    <row r="2" spans="1:35">
-      <c r="A2" s="46" t="s">
+    <row r="2" spans="1:35" ht="15" customHeight="1">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="31"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="29"/>
       <c r="S2" s="18"/>
       <c r="T2" s="18"/>
       <c r="U2" s="18"/>
       <c r="V2" s="18"/>
       <c r="W2" s="18"/>
-      <c r="X2" s="38"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="40"/>
-    </row>
-    <row r="3" spans="1:35">
-      <c r="A3" s="46" t="s">
+      <c r="X2" s="40"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="42"/>
+    </row>
+    <row r="3" spans="1:35" ht="15" customHeight="1">
+      <c r="A3" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="49"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="33"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
-      <c r="O3" s="33"/>
-      <c r="P3" s="33"/>
-      <c r="Q3" s="33"/>
-      <c r="R3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="32"/>
       <c r="S3" s="18"/>
       <c r="T3" s="18"/>
       <c r="U3" s="18"/>
       <c r="V3" s="18"/>
       <c r="W3" s="18"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="42"/>
-      <c r="Z3" s="43"/>
+      <c r="X3" s="43"/>
+      <c r="Y3" s="44"/>
+      <c r="Z3" s="45"/>
     </row>
     <row r="4" spans="1:35" s="12" customFormat="1" ht="30.75">
       <c r="A4" s="13" t="s">
@@ -1236,82 +1272,82 @@
       </c>
     </row>
     <row r="5" spans="1:35" s="12" customFormat="1">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="24">
         <v>46203</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="24">
         <v>48029</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="21">
         <f>DATEDIF(G5, H5, "Y")</f>
         <v>5</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="21">
         <v>45625</v>
       </c>
-      <c r="K5" s="23" t="b">
+      <c r="K5" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="L5" s="23" t="b">
-        <v>0</v>
-      </c>
-      <c r="M5" s="23" t="b">
+      <c r="L5" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="N5" s="22" t="s">
+      <c r="N5" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="O5" s="22" t="s">
+      <c r="O5" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="P5" s="22" t="s">
+      <c r="P5" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="Q5" s="22" t="s">
+      <c r="Q5" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="R5" s="22" t="s">
+      <c r="R5" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="S5" s="24">
+      <c r="S5" s="23">
         <f>IFERROR(VLOOKUP(N5,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v>105</v>
       </c>
-      <c r="T5" s="24">
+      <c r="T5" s="23">
         <f>IFERROR(VLOOKUP(O5,Scoring!$C$12:$E$15,2,FALSE),"")</f>
         <v>125</v>
       </c>
-      <c r="U5" s="24">
+      <c r="U5" s="23">
         <f>IFERROR(VLOOKUP(P5,Scoring!$C$17:$E$20,2,FALSE),"")</f>
         <v>50</v>
       </c>
-      <c r="V5" s="24">
+      <c r="V5" s="23">
         <f>IFERROR(VLOOKUP(Q5,Scoring!$C$22:$E$25,2,FALSE),"")</f>
         <v>100</v>
       </c>
-      <c r="W5" s="24">
+      <c r="W5" s="23">
         <f>IFERROR(VLOOKUP(R5,Scoring!$C$27:$E$30,2,FALSE),"")</f>
         <v>50</v>
       </c>
-      <c r="X5" s="24">
+      <c r="X5" s="23">
         <f t="shared" ref="X5" si="0">SUM(S5:W5)</f>
         <v>430</v>
       </c>
@@ -1325,35 +1361,35 @@
       </c>
     </row>
     <row r="6" spans="1:35">
-      <c r="A6" s="19">
+      <c r="A6" s="26">
         <v>1</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="45">
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="25"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="25">
         <f>DATEDIF(G6, H6, "Y")</f>
         <v>0</v>
       </c>
-      <c r="J6" s="19"/>
-      <c r="K6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="26"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
+      <c r="R6" s="26"/>
       <c r="S6" s="7" t="str">
         <f>IFERROR(VLOOKUP(N6,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1388,35 +1424,35 @@
       </c>
     </row>
     <row r="7" spans="1:35">
-      <c r="A7" s="19">
+      <c r="A7" s="26">
         <v>2</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="45">
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="25">
         <f t="shared" ref="I7:I69" si="6">DATEDIF(G7, H7, "Y")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="19"/>
-      <c r="K7" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L7" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M7" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="P7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L7" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="26"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
       <c r="S7" s="7" t="str">
         <f>IFERROR(VLOOKUP(N7,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1451,35 +1487,35 @@
       </c>
     </row>
     <row r="8" spans="1:35">
-      <c r="A8" s="19">
+      <c r="A8" s="26">
         <v>3</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="45">
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="26"/>
+      <c r="H8" s="26"/>
+      <c r="I8" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
+      <c r="J8" s="26"/>
+      <c r="K8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
+      <c r="R8" s="26"/>
       <c r="S8" s="7" t="str">
         <f>IFERROR(VLOOKUP(N8,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1514,35 +1550,35 @@
       </c>
     </row>
     <row r="9" spans="1:35">
-      <c r="A9" s="19">
+      <c r="A9" s="26">
         <v>4</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="45">
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J9" s="19"/>
-      <c r="K9" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M9" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L9" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
       <c r="S9" s="7" t="str">
         <f>IFERROR(VLOOKUP(N9,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1577,35 +1613,35 @@
       </c>
     </row>
     <row r="10" spans="1:35">
-      <c r="A10" s="19">
+      <c r="A10" s="26">
         <v>5</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="45">
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J10" s="19"/>
-      <c r="K10" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N10" s="19"/>
-      <c r="O10" s="19"/>
-      <c r="P10" s="19"/>
-      <c r="Q10" s="19"/>
-      <c r="R10" s="19"/>
+      <c r="J10" s="26"/>
+      <c r="K10" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L10" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
       <c r="S10" s="7" t="str">
         <f>IFERROR(VLOOKUP(N10,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1640,35 +1676,35 @@
       </c>
     </row>
     <row r="11" spans="1:35">
-      <c r="A11" s="19">
+      <c r="A11" s="26">
         <v>6</v>
       </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="45">
+      <c r="B11" s="26"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M11" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19"/>
-      <c r="P11" s="19"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
       <c r="S11" s="7" t="str">
         <f>IFERROR(VLOOKUP(N11,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1703,35 +1739,35 @@
       </c>
     </row>
     <row r="12" spans="1:35">
-      <c r="A12" s="19">
+      <c r="A12" s="26">
         <v>7</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="45">
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J12" s="19"/>
-      <c r="K12" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" s="19"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
-      <c r="Q12" s="19"/>
-      <c r="R12" s="19"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="26"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="26"/>
+      <c r="Q12" s="26"/>
+      <c r="R12" s="26"/>
       <c r="S12" s="7" t="str">
         <f>IFERROR(VLOOKUP(N12,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1766,35 +1802,35 @@
       </c>
     </row>
     <row r="13" spans="1:35">
-      <c r="A13" s="19">
+      <c r="A13" s="26">
         <v>8</v>
       </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="45">
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J13" s="19"/>
-      <c r="K13" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M13" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L13" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
       <c r="S13" s="7" t="str">
         <f>IFERROR(VLOOKUP(N13,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1829,35 +1865,35 @@
       </c>
     </row>
     <row r="14" spans="1:35">
-      <c r="A14" s="19">
+      <c r="A14" s="26">
         <v>9</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="45">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J14" s="19"/>
-      <c r="K14" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N14" s="19"/>
-      <c r="O14" s="19"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="19"/>
-      <c r="R14" s="19"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
       <c r="S14" s="7" t="str">
         <f>IFERROR(VLOOKUP(N14,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1892,35 +1928,35 @@
       </c>
     </row>
     <row r="15" spans="1:35">
-      <c r="A15" s="19">
+      <c r="A15" s="26">
         <v>10</v>
       </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="45">
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J15" s="19"/>
-      <c r="K15" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N15" s="19"/>
-      <c r="O15" s="19"/>
-      <c r="P15" s="19"/>
-      <c r="Q15" s="19"/>
-      <c r="R15" s="19"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L15" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
       <c r="S15" s="7" t="str">
         <f>IFERROR(VLOOKUP(N15,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -1955,35 +1991,35 @@
       </c>
     </row>
     <row r="16" spans="1:35">
-      <c r="A16" s="19">
+      <c r="A16" s="26">
         <v>11</v>
       </c>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="45">
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J16" s="19"/>
-      <c r="K16" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="19"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L16" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
       <c r="S16" s="7" t="str">
         <f>IFERROR(VLOOKUP(N16,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2018,35 +2054,35 @@
       </c>
     </row>
     <row r="17" spans="1:26">
-      <c r="A17" s="19">
+      <c r="A17" s="26">
         <v>12</v>
       </c>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="45">
+      <c r="B17" s="26"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J17" s="19"/>
-      <c r="K17" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L17" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L17" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="26"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="26"/>
+      <c r="Q17" s="26"/>
+      <c r="R17" s="26"/>
       <c r="S17" s="7" t="str">
         <f>IFERROR(VLOOKUP(N17,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2081,35 +2117,35 @@
       </c>
     </row>
     <row r="18" spans="1:26">
-      <c r="A18" s="19">
+      <c r="A18" s="26">
         <v>13</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="45">
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J18" s="19"/>
-      <c r="K18" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
       <c r="S18" s="7" t="str">
         <f>IFERROR(VLOOKUP(N18,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2144,35 +2180,35 @@
       </c>
     </row>
     <row r="19" spans="1:26">
-      <c r="A19" s="19">
+      <c r="A19" s="26">
         <v>14</v>
       </c>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="45">
+      <c r="B19" s="26"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J19" s="19"/>
-      <c r="K19" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="26"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="26"/>
+      <c r="R19" s="26"/>
       <c r="S19" s="7" t="str">
         <f>IFERROR(VLOOKUP(N19,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2207,35 +2243,35 @@
       </c>
     </row>
     <row r="20" spans="1:26">
-      <c r="A20" s="19">
+      <c r="A20" s="26">
         <v>15</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="45">
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J20" s="19"/>
-      <c r="K20" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L20" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="26"/>
+      <c r="Q20" s="26"/>
+      <c r="R20" s="26"/>
       <c r="S20" s="7" t="str">
         <f>IFERROR(VLOOKUP(N20,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2270,35 +2306,35 @@
       </c>
     </row>
     <row r="21" spans="1:26">
-      <c r="A21" s="19">
+      <c r="A21" s="26">
         <v>16</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="45">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J21" s="19"/>
-      <c r="K21" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M21" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L21" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
       <c r="S21" s="7" t="str">
         <f>IFERROR(VLOOKUP(N21,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2333,35 +2369,35 @@
       </c>
     </row>
     <row r="22" spans="1:26">
-      <c r="A22" s="19">
+      <c r="A22" s="26">
         <v>17</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="45">
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J22" s="19"/>
-      <c r="K22" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
       <c r="S22" s="7" t="str">
         <f>IFERROR(VLOOKUP(N22,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2396,35 +2432,35 @@
       </c>
     </row>
     <row r="23" spans="1:26">
-      <c r="A23" s="19">
+      <c r="A23" s="26">
         <v>18</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="45">
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J23" s="19"/>
-      <c r="K23" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M23" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
       <c r="S23" s="7" t="str">
         <f>IFERROR(VLOOKUP(N23,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2459,35 +2495,35 @@
       </c>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="19">
+      <c r="A24" s="26">
         <v>19</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="45">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L24" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
       <c r="S24" s="7" t="str">
         <f>IFERROR(VLOOKUP(N24,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2522,35 +2558,35 @@
       </c>
     </row>
     <row r="25" spans="1:26">
-      <c r="A25" s="19">
+      <c r="A25" s="26">
         <v>20</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="45">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J25" s="19"/>
-      <c r="K25" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L25" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M25" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="P25" s="19"/>
-      <c r="Q25" s="19"/>
-      <c r="R25" s="19"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
       <c r="S25" s="7" t="str">
         <f>IFERROR(VLOOKUP(N25,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2585,35 +2621,35 @@
       </c>
     </row>
     <row r="26" spans="1:26">
-      <c r="A26" s="19">
+      <c r="A26" s="26">
         <v>21</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="45">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L26" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M26" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26" s="19"/>
-      <c r="O26" s="19"/>
-      <c r="P26" s="19"/>
-      <c r="Q26" s="19"/>
-      <c r="R26" s="19"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
       <c r="S26" s="7" t="str">
         <f>IFERROR(VLOOKUP(N26,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2648,35 +2684,35 @@
       </c>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="19">
+      <c r="A27" s="26">
         <v>22</v>
       </c>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="45">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J27" s="19"/>
-      <c r="K27" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L27" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M27" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="P27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
       <c r="S27" s="7" t="str">
         <f>IFERROR(VLOOKUP(N27,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2711,35 +2747,35 @@
       </c>
     </row>
     <row r="28" spans="1:26">
-      <c r="A28" s="19">
+      <c r="A28" s="26">
         <v>23</v>
       </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="45">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J28" s="19"/>
-      <c r="K28" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L28" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M28" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" s="19"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="19"/>
-      <c r="Q28" s="19"/>
-      <c r="R28" s="19"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
       <c r="S28" s="7" t="str">
         <f>IFERROR(VLOOKUP(N28,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2774,35 +2810,35 @@
       </c>
     </row>
     <row r="29" spans="1:26">
-      <c r="A29" s="19">
+      <c r="A29" s="26">
         <v>24</v>
       </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="45">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J29" s="19"/>
-      <c r="K29" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M29" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="P29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
       <c r="S29" s="7" t="str">
         <f>IFERROR(VLOOKUP(N29,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2837,35 +2873,35 @@
       </c>
     </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="19">
+      <c r="A30" s="26">
         <v>25</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="45">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J30" s="19"/>
-      <c r="K30" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L30" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M30" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N30" s="19"/>
-      <c r="O30" s="19"/>
-      <c r="P30" s="19"/>
-      <c r="Q30" s="19"/>
-      <c r="R30" s="19"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
       <c r="S30" s="7" t="str">
         <f>IFERROR(VLOOKUP(N30,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2900,35 +2936,35 @@
       </c>
     </row>
     <row r="31" spans="1:26">
-      <c r="A31" s="19">
+      <c r="A31" s="26">
         <v>26</v>
       </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="45">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="25"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J31" s="19"/>
-      <c r="K31" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M31" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="P31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L31" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
       <c r="S31" s="7" t="str">
         <f>IFERROR(VLOOKUP(N31,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -2963,35 +2999,35 @@
       </c>
     </row>
     <row r="32" spans="1:26">
-      <c r="A32" s="19">
+      <c r="A32" s="26">
         <v>27</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="45">
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J32" s="19"/>
-      <c r="K32" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M32" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N32" s="19"/>
-      <c r="O32" s="19"/>
-      <c r="P32" s="19"/>
-      <c r="Q32" s="19"/>
-      <c r="R32" s="19"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
       <c r="S32" s="7" t="str">
         <f>IFERROR(VLOOKUP(N32,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3026,35 +3062,35 @@
       </c>
     </row>
     <row r="33" spans="1:26">
-      <c r="A33" s="19">
+      <c r="A33" s="26">
         <v>28</v>
       </c>
-      <c r="B33" s="19"/>
-      <c r="C33" s="19"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="45">
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J33" s="19"/>
-      <c r="K33" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M33" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
       <c r="S33" s="7" t="str">
         <f>IFERROR(VLOOKUP(N33,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3089,35 +3125,35 @@
       </c>
     </row>
     <row r="34" spans="1:26">
-      <c r="A34" s="19">
+      <c r="A34" s="26">
         <v>29</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="45">
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J34" s="19"/>
-      <c r="K34" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M34" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N34" s="19"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="19"/>
-      <c r="Q34" s="19"/>
-      <c r="R34" s="19"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
       <c r="S34" s="7" t="str">
         <f>IFERROR(VLOOKUP(N34,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3152,35 +3188,35 @@
       </c>
     </row>
     <row r="35" spans="1:26">
-      <c r="A35" s="19">
+      <c r="A35" s="26">
         <v>30</v>
       </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="45">
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J35" s="19"/>
-      <c r="K35" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L35" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N35" s="19"/>
-      <c r="O35" s="19"/>
-      <c r="P35" s="19"/>
-      <c r="Q35" s="19"/>
-      <c r="R35" s="19"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="26"/>
       <c r="S35" s="7" t="str">
         <f>IFERROR(VLOOKUP(N35,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3215,35 +3251,35 @@
       </c>
     </row>
     <row r="36" spans="1:26">
-      <c r="A36" s="19">
+      <c r="A36" s="26">
         <v>31</v>
       </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="19"/>
-      <c r="H36" s="19"/>
-      <c r="I36" s="45">
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J36" s="19"/>
-      <c r="K36" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L36" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M36" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N36" s="19"/>
-      <c r="O36" s="19"/>
-      <c r="P36" s="19"/>
-      <c r="Q36" s="19"/>
-      <c r="R36" s="19"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
       <c r="S36" s="7" t="str">
         <f>IFERROR(VLOOKUP(N36,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3278,35 +3314,35 @@
       </c>
     </row>
     <row r="37" spans="1:26">
-      <c r="A37" s="19">
+      <c r="A37" s="26">
         <v>32</v>
       </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="19"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="45">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J37" s="19"/>
-      <c r="K37" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M37" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N37" s="19"/>
-      <c r="O37" s="19"/>
-      <c r="P37" s="19"/>
-      <c r="Q37" s="19"/>
-      <c r="R37" s="19"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
       <c r="S37" s="7" t="str">
         <f>IFERROR(VLOOKUP(N37,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3341,35 +3377,35 @@
       </c>
     </row>
     <row r="38" spans="1:26">
-      <c r="A38" s="19">
+      <c r="A38" s="26">
         <v>33</v>
       </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="19"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="45">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J38" s="19"/>
-      <c r="K38" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M38" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N38" s="19"/>
-      <c r="O38" s="19"/>
-      <c r="P38" s="19"/>
-      <c r="Q38" s="19"/>
-      <c r="R38" s="19"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
       <c r="S38" s="7" t="str">
         <f>IFERROR(VLOOKUP(N38,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3404,35 +3440,35 @@
       </c>
     </row>
     <row r="39" spans="1:26">
-      <c r="A39" s="19">
+      <c r="A39" s="26">
         <v>34</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="45">
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J39" s="19"/>
-      <c r="K39" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
-      <c r="Q39" s="19"/>
-      <c r="R39" s="19"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
       <c r="S39" s="7" t="str">
         <f>IFERROR(VLOOKUP(N39,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3467,35 +3503,35 @@
       </c>
     </row>
     <row r="40" spans="1:26">
-      <c r="A40" s="19">
+      <c r="A40" s="26">
         <v>35</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="45">
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J40" s="19"/>
-      <c r="K40" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M40" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N40" s="19"/>
-      <c r="O40" s="19"/>
-      <c r="P40" s="19"/>
-      <c r="Q40" s="19"/>
-      <c r="R40" s="19"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="26"/>
       <c r="S40" s="7" t="str">
         <f>IFERROR(VLOOKUP(N40,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3530,35 +3566,35 @@
       </c>
     </row>
     <row r="41" spans="1:26">
-      <c r="A41" s="19">
+      <c r="A41" s="26">
         <v>36</v>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="45">
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J41" s="19"/>
-      <c r="K41" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M41" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N41" s="19"/>
-      <c r="O41" s="19"/>
-      <c r="P41" s="19"/>
-      <c r="Q41" s="19"/>
-      <c r="R41" s="19"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="26"/>
       <c r="S41" s="7" t="str">
         <f>IFERROR(VLOOKUP(N41,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3593,35 +3629,35 @@
       </c>
     </row>
     <row r="42" spans="1:26">
-      <c r="A42" s="19">
+      <c r="A42" s="26">
         <v>37</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="45">
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J42" s="19"/>
-      <c r="K42" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M42" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
       <c r="S42" s="7" t="str">
         <f>IFERROR(VLOOKUP(N42,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3656,35 +3692,35 @@
       </c>
     </row>
     <row r="43" spans="1:26">
-      <c r="A43" s="19">
+      <c r="A43" s="26">
         <v>38</v>
       </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="45">
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J43" s="19"/>
-      <c r="K43" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M43" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N43" s="19"/>
-      <c r="O43" s="19"/>
-      <c r="P43" s="19"/>
-      <c r="Q43" s="19"/>
-      <c r="R43" s="19"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
       <c r="S43" s="7" t="str">
         <f>IFERROR(VLOOKUP(N43,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3719,35 +3755,35 @@
       </c>
     </row>
     <row r="44" spans="1:26">
-      <c r="A44" s="19">
+      <c r="A44" s="26">
         <v>39</v>
       </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="45">
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J44" s="19"/>
-      <c r="K44" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M44" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N44" s="19"/>
-      <c r="O44" s="19"/>
-      <c r="P44" s="19"/>
-      <c r="Q44" s="19"/>
-      <c r="R44" s="19"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
       <c r="S44" s="7" t="str">
         <f>IFERROR(VLOOKUP(N44,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3782,35 +3818,35 @@
       </c>
     </row>
     <row r="45" spans="1:26">
-      <c r="A45" s="19">
+      <c r="A45" s="26">
         <v>40</v>
       </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="45">
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="25"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J45" s="19"/>
-      <c r="K45" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M45" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N45" s="19"/>
-      <c r="O45" s="19"/>
-      <c r="P45" s="19"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="19"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" s="26"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="26"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="26"/>
       <c r="S45" s="7" t="str">
         <f>IFERROR(VLOOKUP(N45,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3845,35 +3881,35 @@
       </c>
     </row>
     <row r="46" spans="1:26">
-      <c r="A46" s="19">
+      <c r="A46" s="26">
         <v>41</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
-      <c r="G46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="45">
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J46" s="19"/>
-      <c r="K46" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M46" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N46" s="19"/>
-      <c r="O46" s="19"/>
-      <c r="P46" s="19"/>
-      <c r="Q46" s="19"/>
-      <c r="R46" s="19"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="26"/>
       <c r="S46" s="7" t="str">
         <f>IFERROR(VLOOKUP(N46,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3908,35 +3944,35 @@
       </c>
     </row>
     <row r="47" spans="1:26">
-      <c r="A47" s="19">
+      <c r="A47" s="26">
         <v>42</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-      <c r="F47" s="19"/>
-      <c r="G47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="45">
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J47" s="19"/>
-      <c r="K47" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M47" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N47" s="19"/>
-      <c r="O47" s="19"/>
-      <c r="P47" s="19"/>
-      <c r="Q47" s="19"/>
-      <c r="R47" s="19"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" s="26"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="26"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="26"/>
       <c r="S47" s="7" t="str">
         <f>IFERROR(VLOOKUP(N47,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -3971,35 +4007,35 @@
       </c>
     </row>
     <row r="48" spans="1:26">
-      <c r="A48" s="19">
+      <c r="A48" s="26">
         <v>43</v>
       </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-      <c r="F48" s="19"/>
-      <c r="G48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="45">
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="25"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J48" s="19"/>
-      <c r="K48" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N48" s="19"/>
-      <c r="O48" s="19"/>
-      <c r="P48" s="19"/>
-      <c r="Q48" s="19"/>
-      <c r="R48" s="19"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="26"/>
       <c r="S48" s="7" t="str">
         <f>IFERROR(VLOOKUP(N48,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4034,35 +4070,35 @@
       </c>
     </row>
     <row r="49" spans="1:26">
-      <c r="A49" s="19">
+      <c r="A49" s="26">
         <v>44</v>
       </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="45">
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="25"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J49" s="19"/>
-      <c r="K49" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M49" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N49" s="19"/>
-      <c r="O49" s="19"/>
-      <c r="P49" s="19"/>
-      <c r="Q49" s="19"/>
-      <c r="R49" s="19"/>
+      <c r="J49" s="26"/>
+      <c r="K49" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" s="26"/>
+      <c r="O49" s="26"/>
+      <c r="P49" s="26"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="26"/>
       <c r="S49" s="7" t="str">
         <f>IFERROR(VLOOKUP(N49,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4097,35 +4133,35 @@
       </c>
     </row>
     <row r="50" spans="1:26">
-      <c r="A50" s="19">
+      <c r="A50" s="26">
         <v>45</v>
       </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-      <c r="F50" s="19"/>
-      <c r="G50" s="19"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="45">
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="25"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J50" s="19"/>
-      <c r="K50" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L50" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M50" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N50" s="19"/>
-      <c r="O50" s="19"/>
-      <c r="P50" s="19"/>
-      <c r="Q50" s="19"/>
-      <c r="R50" s="19"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" s="26"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="26"/>
+      <c r="Q50" s="26"/>
+      <c r="R50" s="26"/>
       <c r="S50" s="7" t="str">
         <f>IFERROR(VLOOKUP(N50,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4160,35 +4196,35 @@
       </c>
     </row>
     <row r="51" spans="1:26">
-      <c r="A51" s="19">
+      <c r="A51" s="26">
         <v>46</v>
       </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-      <c r="F51" s="19"/>
-      <c r="G51" s="19"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="45">
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J51" s="19"/>
-      <c r="K51" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N51" s="19"/>
-      <c r="O51" s="19"/>
-      <c r="P51" s="19"/>
-      <c r="Q51" s="19"/>
-      <c r="R51" s="19"/>
+      <c r="J51" s="26"/>
+      <c r="K51" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" s="26"/>
+      <c r="O51" s="26"/>
+      <c r="P51" s="26"/>
+      <c r="Q51" s="26"/>
+      <c r="R51" s="26"/>
       <c r="S51" s="7" t="str">
         <f>IFERROR(VLOOKUP(N51,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4223,35 +4259,35 @@
       </c>
     </row>
     <row r="52" spans="1:26">
-      <c r="A52" s="19">
+      <c r="A52" s="26">
         <v>47</v>
       </c>
-      <c r="B52" s="19"/>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="45">
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="25"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J52" s="19"/>
-      <c r="K52" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M52" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N52" s="19"/>
-      <c r="O52" s="19"/>
-      <c r="P52" s="19"/>
-      <c r="Q52" s="19"/>
-      <c r="R52" s="19"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="26"/>
+      <c r="Q52" s="26"/>
+      <c r="R52" s="26"/>
       <c r="S52" s="7" t="str">
         <f>IFERROR(VLOOKUP(N52,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4286,35 +4322,35 @@
       </c>
     </row>
     <row r="53" spans="1:26">
-      <c r="A53" s="19">
+      <c r="A53" s="26">
         <v>48</v>
       </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="45">
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="25"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J53" s="19"/>
-      <c r="K53" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M53" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N53" s="19"/>
-      <c r="O53" s="19"/>
-      <c r="P53" s="19"/>
-      <c r="Q53" s="19"/>
-      <c r="R53" s="19"/>
+      <c r="J53" s="26"/>
+      <c r="K53" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" s="26"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="26"/>
+      <c r="Q53" s="26"/>
+      <c r="R53" s="26"/>
       <c r="S53" s="7" t="str">
         <f>IFERROR(VLOOKUP(N53,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4349,35 +4385,35 @@
       </c>
     </row>
     <row r="54" spans="1:26">
-      <c r="A54" s="19">
+      <c r="A54" s="26">
         <v>49</v>
       </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="45">
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="26"/>
+      <c r="F54" s="25"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J54" s="19"/>
-      <c r="K54" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L54" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M54" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N54" s="19"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="19"/>
-      <c r="Q54" s="19"/>
-      <c r="R54" s="19"/>
+      <c r="J54" s="26"/>
+      <c r="K54" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" s="26"/>
+      <c r="O54" s="26"/>
+      <c r="P54" s="26"/>
+      <c r="Q54" s="26"/>
+      <c r="R54" s="26"/>
       <c r="S54" s="7" t="str">
         <f>IFERROR(VLOOKUP(N54,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4412,35 +4448,35 @@
       </c>
     </row>
     <row r="55" spans="1:26">
-      <c r="A55" s="19">
+      <c r="A55" s="26">
         <v>50</v>
       </c>
-      <c r="B55" s="19"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="45">
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="26"/>
+      <c r="F55" s="25"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J55" s="19"/>
-      <c r="K55" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L55" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M55" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N55" s="19"/>
-      <c r="O55" s="19"/>
-      <c r="P55" s="19"/>
-      <c r="Q55" s="19"/>
-      <c r="R55" s="19"/>
+      <c r="J55" s="26"/>
+      <c r="K55" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" s="26"/>
+      <c r="O55" s="26"/>
+      <c r="P55" s="26"/>
+      <c r="Q55" s="26"/>
+      <c r="R55" s="26"/>
       <c r="S55" s="7" t="str">
         <f>IFERROR(VLOOKUP(N55,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4475,35 +4511,35 @@
       </c>
     </row>
     <row r="56" spans="1:26">
-      <c r="A56" s="19">
+      <c r="A56" s="26">
         <v>51</v>
       </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-      <c r="F56" s="19"/>
-      <c r="G56" s="19"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="45">
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J56" s="19"/>
-      <c r="K56" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L56" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M56" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N56" s="19"/>
-      <c r="O56" s="19"/>
-      <c r="P56" s="19"/>
-      <c r="Q56" s="19"/>
-      <c r="R56" s="19"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" s="26"/>
+      <c r="O56" s="26"/>
+      <c r="P56" s="26"/>
+      <c r="Q56" s="26"/>
+      <c r="R56" s="26"/>
       <c r="S56" s="7" t="str">
         <f>IFERROR(VLOOKUP(N56,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4538,35 +4574,35 @@
       </c>
     </row>
     <row r="57" spans="1:26">
-      <c r="A57" s="19">
+      <c r="A57" s="26">
         <v>52</v>
       </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="45">
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="25"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J57" s="19"/>
-      <c r="K57" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L57" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M57" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N57" s="19"/>
-      <c r="O57" s="19"/>
-      <c r="P57" s="19"/>
-      <c r="Q57" s="19"/>
-      <c r="R57" s="19"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" s="26"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="26"/>
+      <c r="Q57" s="26"/>
+      <c r="R57" s="26"/>
       <c r="S57" s="7" t="str">
         <f>IFERROR(VLOOKUP(N57,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4601,35 +4637,35 @@
       </c>
     </row>
     <row r="58" spans="1:26">
-      <c r="A58" s="19">
+      <c r="A58" s="26">
         <v>53</v>
       </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="45">
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="25"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J58" s="19"/>
-      <c r="K58" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L58" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M58" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N58" s="19"/>
-      <c r="O58" s="19"/>
-      <c r="P58" s="19"/>
-      <c r="Q58" s="19"/>
-      <c r="R58" s="19"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" s="26"/>
+      <c r="O58" s="26"/>
+      <c r="P58" s="26"/>
+      <c r="Q58" s="26"/>
+      <c r="R58" s="26"/>
       <c r="S58" s="7" t="str">
         <f>IFERROR(VLOOKUP(N58,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4664,35 +4700,35 @@
       </c>
     </row>
     <row r="59" spans="1:26">
-      <c r="A59" s="19">
+      <c r="A59" s="26">
         <v>54</v>
       </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="45">
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="25"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J59" s="19"/>
-      <c r="K59" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L59" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M59" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N59" s="19"/>
-      <c r="O59" s="19"/>
-      <c r="P59" s="19"/>
-      <c r="Q59" s="19"/>
-      <c r="R59" s="19"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" s="26"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="26"/>
+      <c r="Q59" s="26"/>
+      <c r="R59" s="26"/>
       <c r="S59" s="7" t="str">
         <f>IFERROR(VLOOKUP(N59,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4727,35 +4763,35 @@
       </c>
     </row>
     <row r="60" spans="1:26">
-      <c r="A60" s="19">
+      <c r="A60" s="26">
         <v>55</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="45">
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="25"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J60" s="19"/>
-      <c r="K60" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L60" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M60" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N60" s="19"/>
-      <c r="O60" s="19"/>
-      <c r="P60" s="19"/>
-      <c r="Q60" s="19"/>
-      <c r="R60" s="19"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L60" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" s="26"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="26"/>
+      <c r="Q60" s="26"/>
+      <c r="R60" s="26"/>
       <c r="S60" s="7" t="str">
         <f>IFERROR(VLOOKUP(N60,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4790,35 +4826,35 @@
       </c>
     </row>
     <row r="61" spans="1:26">
-      <c r="A61" s="19">
+      <c r="A61" s="26">
         <v>56</v>
       </c>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="45">
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="25"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J61" s="19"/>
-      <c r="K61" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M61" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N61" s="19"/>
-      <c r="O61" s="19"/>
-      <c r="P61" s="19"/>
-      <c r="Q61" s="19"/>
-      <c r="R61" s="19"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
+      <c r="R61" s="26"/>
       <c r="S61" s="7" t="str">
         <f>IFERROR(VLOOKUP(N61,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4853,35 +4889,35 @@
       </c>
     </row>
     <row r="62" spans="1:26">
-      <c r="A62" s="19">
+      <c r="A62" s="26">
         <v>57</v>
       </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="45">
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="25"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J62" s="19"/>
-      <c r="K62" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L62" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M62" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N62" s="19"/>
-      <c r="O62" s="19"/>
-      <c r="P62" s="19"/>
-      <c r="Q62" s="19"/>
-      <c r="R62" s="19"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" s="26"/>
+      <c r="O62" s="26"/>
+      <c r="P62" s="26"/>
+      <c r="Q62" s="26"/>
+      <c r="R62" s="26"/>
       <c r="S62" s="7" t="str">
         <f>IFERROR(VLOOKUP(N62,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4916,35 +4952,35 @@
       </c>
     </row>
     <row r="63" spans="1:26">
-      <c r="A63" s="19">
+      <c r="A63" s="26">
         <v>58</v>
       </c>
-      <c r="B63" s="19"/>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19"/>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19"/>
-      <c r="I63" s="45">
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J63" s="19"/>
-      <c r="K63" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L63" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M63" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N63" s="19"/>
-      <c r="O63" s="19"/>
-      <c r="P63" s="19"/>
-      <c r="Q63" s="19"/>
-      <c r="R63" s="19"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="26"/>
+      <c r="Q63" s="26"/>
+      <c r="R63" s="26"/>
       <c r="S63" s="7" t="str">
         <f>IFERROR(VLOOKUP(N63,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -4979,35 +5015,35 @@
       </c>
     </row>
     <row r="64" spans="1:26">
-      <c r="A64" s="19">
+      <c r="A64" s="26">
         <v>59</v>
       </c>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-      <c r="F64" s="19"/>
-      <c r="G64" s="19"/>
-      <c r="H64" s="19"/>
-      <c r="I64" s="45">
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J64" s="19"/>
-      <c r="K64" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L64" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M64" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N64" s="19"/>
-      <c r="O64" s="19"/>
-      <c r="P64" s="19"/>
-      <c r="Q64" s="19"/>
-      <c r="R64" s="19"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" s="26"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="26"/>
+      <c r="Q64" s="26"/>
+      <c r="R64" s="26"/>
       <c r="S64" s="7" t="str">
         <f>IFERROR(VLOOKUP(N64,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5042,35 +5078,35 @@
       </c>
     </row>
     <row r="65" spans="1:26">
-      <c r="A65" s="19">
+      <c r="A65" s="26">
         <v>60</v>
       </c>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
-      <c r="G65" s="19"/>
-      <c r="H65" s="19"/>
-      <c r="I65" s="45">
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="25"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J65" s="19"/>
-      <c r="K65" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L65" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M65" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N65" s="19"/>
-      <c r="O65" s="19"/>
-      <c r="P65" s="19"/>
-      <c r="Q65" s="19"/>
-      <c r="R65" s="19"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
+      <c r="Q65" s="26"/>
+      <c r="R65" s="26"/>
       <c r="S65" s="7" t="str">
         <f>IFERROR(VLOOKUP(N65,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5105,35 +5141,35 @@
       </c>
     </row>
     <row r="66" spans="1:26">
-      <c r="A66" s="19">
+      <c r="A66" s="26">
         <v>61</v>
       </c>
-      <c r="B66" s="19"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-      <c r="F66" s="19"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="45">
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="25"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J66" s="19"/>
-      <c r="K66" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L66" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M66" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N66" s="19"/>
-      <c r="O66" s="19"/>
-      <c r="P66" s="19"/>
-      <c r="Q66" s="19"/>
-      <c r="R66" s="19"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" s="26"/>
+      <c r="O66" s="26"/>
+      <c r="P66" s="26"/>
+      <c r="Q66" s="26"/>
+      <c r="R66" s="26"/>
       <c r="S66" s="7" t="str">
         <f>IFERROR(VLOOKUP(N66,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5168,35 +5204,35 @@
       </c>
     </row>
     <row r="67" spans="1:26">
-      <c r="A67" s="19">
+      <c r="A67" s="26">
         <v>62</v>
       </c>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-      <c r="F67" s="19"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="45">
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="26"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J67" s="19"/>
-      <c r="K67" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M67" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N67" s="19"/>
-      <c r="O67" s="19"/>
-      <c r="P67" s="19"/>
-      <c r="Q67" s="19"/>
-      <c r="R67" s="19"/>
+      <c r="J67" s="26"/>
+      <c r="K67" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" s="26"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="26"/>
+      <c r="Q67" s="26"/>
+      <c r="R67" s="26"/>
       <c r="S67" s="7" t="str">
         <f>IFERROR(VLOOKUP(N67,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5231,35 +5267,35 @@
       </c>
     </row>
     <row r="68" spans="1:26">
-      <c r="A68" s="19">
+      <c r="A68" s="26">
         <v>63</v>
       </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="45">
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="26"/>
+      <c r="I68" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J68" s="19"/>
-      <c r="K68" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M68" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N68" s="19"/>
-      <c r="O68" s="19"/>
-      <c r="P68" s="19"/>
-      <c r="Q68" s="19"/>
-      <c r="R68" s="19"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" s="26"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="26"/>
+      <c r="Q68" s="26"/>
+      <c r="R68" s="26"/>
       <c r="S68" s="7" t="str">
         <f>IFERROR(VLOOKUP(N68,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5294,35 +5330,35 @@
       </c>
     </row>
     <row r="69" spans="1:26">
-      <c r="A69" s="19">
+      <c r="A69" s="26">
         <v>64</v>
       </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-      <c r="F69" s="19"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="45">
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="25"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="25">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J69" s="19"/>
-      <c r="K69" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L69" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M69" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N69" s="19"/>
-      <c r="O69" s="19"/>
-      <c r="P69" s="19"/>
-      <c r="Q69" s="19"/>
-      <c r="R69" s="19"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" s="26"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="26"/>
+      <c r="Q69" s="26"/>
+      <c r="R69" s="26"/>
       <c r="S69" s="7" t="str">
         <f>IFERROR(VLOOKUP(N69,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5357,35 +5393,35 @@
       </c>
     </row>
     <row r="70" spans="1:26">
-      <c r="A70" s="19">
+      <c r="A70" s="26">
         <v>65</v>
       </c>
-      <c r="B70" s="19"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-      <c r="F70" s="19"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="45">
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="25"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="25">
         <f t="shared" ref="I70:I105" si="7">DATEDIF(G70, H70, "Y")</f>
         <v>0</v>
       </c>
-      <c r="J70" s="19"/>
-      <c r="K70" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M70" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N70" s="19"/>
-      <c r="O70" s="19"/>
-      <c r="P70" s="19"/>
-      <c r="Q70" s="19"/>
-      <c r="R70" s="19"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+      <c r="Q70" s="26"/>
+      <c r="R70" s="26"/>
       <c r="S70" s="7" t="str">
         <f>IFERROR(VLOOKUP(N70,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5420,35 +5456,35 @@
       </c>
     </row>
     <row r="71" spans="1:26">
-      <c r="A71" s="19">
+      <c r="A71" s="26">
         <v>66</v>
       </c>
-      <c r="B71" s="19"/>
-      <c r="C71" s="19"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-      <c r="F71" s="19"/>
-      <c r="G71" s="19"/>
-      <c r="H71" s="19"/>
-      <c r="I71" s="45">
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="25"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J71" s="19"/>
-      <c r="K71" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M71" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N71" s="19"/>
-      <c r="O71" s="19"/>
-      <c r="P71" s="19"/>
-      <c r="Q71" s="19"/>
-      <c r="R71" s="19"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+      <c r="Q71" s="26"/>
+      <c r="R71" s="26"/>
       <c r="S71" s="7" t="str">
         <f>IFERROR(VLOOKUP(N71,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5483,35 +5519,35 @@
       </c>
     </row>
     <row r="72" spans="1:26">
-      <c r="A72" s="19">
+      <c r="A72" s="26">
         <v>67</v>
       </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-      <c r="F72" s="19"/>
-      <c r="G72" s="19"/>
-      <c r="H72" s="19"/>
-      <c r="I72" s="45">
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J72" s="19"/>
-      <c r="K72" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M72" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N72" s="19"/>
-      <c r="O72" s="19"/>
-      <c r="P72" s="19"/>
-      <c r="Q72" s="19"/>
-      <c r="R72" s="19"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
+      <c r="Q72" s="26"/>
+      <c r="R72" s="26"/>
       <c r="S72" s="7" t="str">
         <f>IFERROR(VLOOKUP(N72,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5546,35 +5582,35 @@
       </c>
     </row>
     <row r="73" spans="1:26">
-      <c r="A73" s="19">
+      <c r="A73" s="26">
         <v>68</v>
       </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
-      <c r="G73" s="19"/>
-      <c r="H73" s="19"/>
-      <c r="I73" s="45">
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="25"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J73" s="19"/>
-      <c r="K73" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N73" s="19"/>
-      <c r="O73" s="19"/>
-      <c r="P73" s="19"/>
-      <c r="Q73" s="19"/>
-      <c r="R73" s="19"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
+      <c r="Q73" s="26"/>
+      <c r="R73" s="26"/>
       <c r="S73" s="7" t="str">
         <f>IFERROR(VLOOKUP(N73,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5609,35 +5645,35 @@
       </c>
     </row>
     <row r="74" spans="1:26">
-      <c r="A74" s="19">
+      <c r="A74" s="26">
         <v>69</v>
       </c>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="45">
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="25"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J74" s="19"/>
-      <c r="K74" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M74" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N74" s="19"/>
-      <c r="O74" s="19"/>
-      <c r="P74" s="19"/>
-      <c r="Q74" s="19"/>
-      <c r="R74" s="19"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L74" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26"/>
+      <c r="Q74" s="26"/>
+      <c r="R74" s="26"/>
       <c r="S74" s="7" t="str">
         <f>IFERROR(VLOOKUP(N74,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5672,35 +5708,35 @@
       </c>
     </row>
     <row r="75" spans="1:26">
-      <c r="A75" s="19">
+      <c r="A75" s="26">
         <v>70</v>
       </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="45">
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="25"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J75" s="19"/>
-      <c r="K75" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M75" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N75" s="19"/>
-      <c r="O75" s="19"/>
-      <c r="P75" s="19"/>
-      <c r="Q75" s="19"/>
-      <c r="R75" s="19"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L75" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26"/>
+      <c r="Q75" s="26"/>
+      <c r="R75" s="26"/>
       <c r="S75" s="7" t="str">
         <f>IFERROR(VLOOKUP(N75,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5735,35 +5771,35 @@
       </c>
     </row>
     <row r="76" spans="1:26">
-      <c r="A76" s="19">
+      <c r="A76" s="26">
         <v>71</v>
       </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="45">
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="25"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J76" s="19"/>
-      <c r="K76" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M76" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N76" s="19"/>
-      <c r="O76" s="19"/>
-      <c r="P76" s="19"/>
-      <c r="Q76" s="19"/>
-      <c r="R76" s="19"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L76" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+      <c r="Q76" s="26"/>
+      <c r="R76" s="26"/>
       <c r="S76" s="7" t="str">
         <f>IFERROR(VLOOKUP(N76,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5798,35 +5834,35 @@
       </c>
     </row>
     <row r="77" spans="1:26">
-      <c r="A77" s="19">
+      <c r="A77" s="26">
         <v>72</v>
       </c>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="45">
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="25"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J77" s="19"/>
-      <c r="K77" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L77" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M77" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N77" s="19"/>
-      <c r="O77" s="19"/>
-      <c r="P77" s="19"/>
-      <c r="Q77" s="19"/>
-      <c r="R77" s="19"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L77" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26"/>
+      <c r="Q77" s="26"/>
+      <c r="R77" s="26"/>
       <c r="S77" s="7" t="str">
         <f>IFERROR(VLOOKUP(N77,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5861,35 +5897,35 @@
       </c>
     </row>
     <row r="78" spans="1:26">
-      <c r="A78" s="19">
+      <c r="A78" s="26">
         <v>73</v>
       </c>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="45">
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="25"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J78" s="19"/>
-      <c r="K78" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M78" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N78" s="19"/>
-      <c r="O78" s="19"/>
-      <c r="P78" s="19"/>
-      <c r="Q78" s="19"/>
-      <c r="R78" s="19"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L78" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
+      <c r="Q78" s="26"/>
+      <c r="R78" s="26"/>
       <c r="S78" s="7" t="str">
         <f>IFERROR(VLOOKUP(N78,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5924,35 +5960,35 @@
       </c>
     </row>
     <row r="79" spans="1:26">
-      <c r="A79" s="19">
+      <c r="A79" s="26">
         <v>74</v>
       </c>
-      <c r="B79" s="19"/>
-      <c r="C79" s="19"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="19"/>
-      <c r="H79" s="19"/>
-      <c r="I79" s="45">
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="25"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J79" s="19"/>
-      <c r="K79" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M79" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N79" s="19"/>
-      <c r="O79" s="19"/>
-      <c r="P79" s="19"/>
-      <c r="Q79" s="19"/>
-      <c r="R79" s="19"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L79" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" s="26"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="26"/>
+      <c r="Q79" s="26"/>
+      <c r="R79" s="26"/>
       <c r="S79" s="7" t="str">
         <f>IFERROR(VLOOKUP(N79,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -5987,35 +6023,35 @@
       </c>
     </row>
     <row r="80" spans="1:26">
-      <c r="A80" s="19">
+      <c r="A80" s="26">
         <v>75</v>
       </c>
-      <c r="B80" s="19"/>
-      <c r="C80" s="19"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
-      <c r="H80" s="19"/>
-      <c r="I80" s="45">
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="25"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J80" s="19"/>
-      <c r="K80" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M80" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N80" s="19"/>
-      <c r="O80" s="19"/>
-      <c r="P80" s="19"/>
-      <c r="Q80" s="19"/>
-      <c r="R80" s="19"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L80" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
+      <c r="R80" s="26"/>
       <c r="S80" s="7" t="str">
         <f>IFERROR(VLOOKUP(N80,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6050,35 +6086,35 @@
       </c>
     </row>
     <row r="81" spans="1:26">
-      <c r="A81" s="19">
+      <c r="A81" s="26">
         <v>76</v>
       </c>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="19"/>
-      <c r="G81" s="19"/>
-      <c r="H81" s="19"/>
-      <c r="I81" s="45">
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="25"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J81" s="19"/>
-      <c r="K81" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L81" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M81" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N81" s="19"/>
-      <c r="O81" s="19"/>
-      <c r="P81" s="19"/>
-      <c r="Q81" s="19"/>
-      <c r="R81" s="19"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L81" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
+      <c r="Q81" s="26"/>
+      <c r="R81" s="26"/>
       <c r="S81" s="7" t="str">
         <f>IFERROR(VLOOKUP(N81,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6113,35 +6149,35 @@
       </c>
     </row>
     <row r="82" spans="1:26">
-      <c r="A82" s="19">
+      <c r="A82" s="26">
         <v>77</v>
       </c>
-      <c r="B82" s="19"/>
-      <c r="C82" s="19"/>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19"/>
-      <c r="F82" s="19"/>
-      <c r="G82" s="19"/>
-      <c r="H82" s="19"/>
-      <c r="I82" s="45">
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J82" s="19"/>
-      <c r="K82" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L82" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M82" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N82" s="19"/>
-      <c r="O82" s="19"/>
-      <c r="P82" s="19"/>
-      <c r="Q82" s="19"/>
-      <c r="R82" s="19"/>
+      <c r="J82" s="26"/>
+      <c r="K82" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L82" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" s="26"/>
+      <c r="O82" s="26"/>
+      <c r="P82" s="26"/>
+      <c r="Q82" s="26"/>
+      <c r="R82" s="26"/>
       <c r="S82" s="7" t="str">
         <f>IFERROR(VLOOKUP(N82,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6176,35 +6212,35 @@
       </c>
     </row>
     <row r="83" spans="1:26">
-      <c r="A83" s="19">
+      <c r="A83" s="26">
         <v>78</v>
       </c>
-      <c r="B83" s="19"/>
-      <c r="C83" s="19"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19"/>
-      <c r="F83" s="19"/>
-      <c r="G83" s="19"/>
-      <c r="H83" s="19"/>
-      <c r="I83" s="45">
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J83" s="19"/>
-      <c r="K83" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M83" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N83" s="19"/>
-      <c r="O83" s="19"/>
-      <c r="P83" s="19"/>
-      <c r="Q83" s="19"/>
-      <c r="R83" s="19"/>
+      <c r="J83" s="26"/>
+      <c r="K83" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L83" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" s="26"/>
+      <c r="O83" s="26"/>
+      <c r="P83" s="26"/>
+      <c r="Q83" s="26"/>
+      <c r="R83" s="26"/>
       <c r="S83" s="7" t="str">
         <f>IFERROR(VLOOKUP(N83,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6239,35 +6275,35 @@
       </c>
     </row>
     <row r="84" spans="1:26">
-      <c r="A84" s="19">
+      <c r="A84" s="26">
         <v>79</v>
       </c>
-      <c r="B84" s="19"/>
-      <c r="C84" s="19"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-      <c r="F84" s="19"/>
-      <c r="G84" s="19"/>
-      <c r="H84" s="19"/>
-      <c r="I84" s="45">
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="25"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J84" s="19"/>
-      <c r="K84" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L84" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M84" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N84" s="19"/>
-      <c r="O84" s="19"/>
-      <c r="P84" s="19"/>
-      <c r="Q84" s="19"/>
-      <c r="R84" s="19"/>
+      <c r="J84" s="26"/>
+      <c r="K84" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L84" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" s="26"/>
+      <c r="O84" s="26"/>
+      <c r="P84" s="26"/>
+      <c r="Q84" s="26"/>
+      <c r="R84" s="26"/>
       <c r="S84" s="7" t="str">
         <f>IFERROR(VLOOKUP(N84,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6302,35 +6338,35 @@
       </c>
     </row>
     <row r="85" spans="1:26">
-      <c r="A85" s="19">
+      <c r="A85" s="26">
         <v>80</v>
       </c>
-      <c r="B85" s="19"/>
-      <c r="C85" s="19"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-      <c r="F85" s="19"/>
-      <c r="G85" s="19"/>
-      <c r="H85" s="19"/>
-      <c r="I85" s="45">
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="25"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J85" s="19"/>
-      <c r="K85" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L85" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M85" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N85" s="19"/>
-      <c r="O85" s="19"/>
-      <c r="P85" s="19"/>
-      <c r="Q85" s="19"/>
-      <c r="R85" s="19"/>
+      <c r="J85" s="26"/>
+      <c r="K85" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L85" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" s="26"/>
+      <c r="O85" s="26"/>
+      <c r="P85" s="26"/>
+      <c r="Q85" s="26"/>
+      <c r="R85" s="26"/>
       <c r="S85" s="7" t="str">
         <f>IFERROR(VLOOKUP(N85,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6365,35 +6401,35 @@
       </c>
     </row>
     <row r="86" spans="1:26">
-      <c r="A86" s="19">
+      <c r="A86" s="26">
         <v>81</v>
       </c>
-      <c r="B86" s="19"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-      <c r="F86" s="19"/>
-      <c r="G86" s="19"/>
-      <c r="H86" s="19"/>
-      <c r="I86" s="45">
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="25"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J86" s="19"/>
-      <c r="K86" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L86" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M86" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N86" s="19"/>
-      <c r="O86" s="19"/>
-      <c r="P86" s="19"/>
-      <c r="Q86" s="19"/>
-      <c r="R86" s="19"/>
+      <c r="J86" s="26"/>
+      <c r="K86" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L86" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" s="26"/>
+      <c r="O86" s="26"/>
+      <c r="P86" s="26"/>
+      <c r="Q86" s="26"/>
+      <c r="R86" s="26"/>
       <c r="S86" s="7" t="str">
         <f>IFERROR(VLOOKUP(N86,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6428,35 +6464,35 @@
       </c>
     </row>
     <row r="87" spans="1:26">
-      <c r="A87" s="19">
+      <c r="A87" s="26">
         <v>82</v>
       </c>
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="19"/>
-      <c r="G87" s="19"/>
-      <c r="H87" s="19"/>
-      <c r="I87" s="45">
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="25"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J87" s="19"/>
-      <c r="K87" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L87" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M87" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N87" s="19"/>
-      <c r="O87" s="19"/>
-      <c r="P87" s="19"/>
-      <c r="Q87" s="19"/>
-      <c r="R87" s="19"/>
+      <c r="J87" s="26"/>
+      <c r="K87" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L87" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" s="26"/>
+      <c r="O87" s="26"/>
+      <c r="P87" s="26"/>
+      <c r="Q87" s="26"/>
+      <c r="R87" s="26"/>
       <c r="S87" s="7" t="str">
         <f>IFERROR(VLOOKUP(N87,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6491,35 +6527,35 @@
       </c>
     </row>
     <row r="88" spans="1:26">
-      <c r="A88" s="19">
+      <c r="A88" s="26">
         <v>83</v>
       </c>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="19"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="19"/>
-      <c r="I88" s="45">
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="26"/>
+      <c r="H88" s="26"/>
+      <c r="I88" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J88" s="19"/>
-      <c r="K88" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L88" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M88" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N88" s="19"/>
-      <c r="O88" s="19"/>
-      <c r="P88" s="19"/>
-      <c r="Q88" s="19"/>
-      <c r="R88" s="19"/>
+      <c r="J88" s="26"/>
+      <c r="K88" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L88" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" s="26"/>
+      <c r="O88" s="26"/>
+      <c r="P88" s="26"/>
+      <c r="Q88" s="26"/>
+      <c r="R88" s="26"/>
       <c r="S88" s="7" t="str">
         <f>IFERROR(VLOOKUP(N88,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6554,35 +6590,35 @@
       </c>
     </row>
     <row r="89" spans="1:26">
-      <c r="A89" s="19">
+      <c r="A89" s="26">
         <v>84</v>
       </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
-      <c r="G89" s="19"/>
-      <c r="H89" s="19"/>
-      <c r="I89" s="45">
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="25"/>
+      <c r="G89" s="26"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J89" s="19"/>
-      <c r="K89" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L89" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M89" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N89" s="19"/>
-      <c r="O89" s="19"/>
-      <c r="P89" s="19"/>
-      <c r="Q89" s="19"/>
-      <c r="R89" s="19"/>
+      <c r="J89" s="26"/>
+      <c r="K89" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L89" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" s="26"/>
+      <c r="O89" s="26"/>
+      <c r="P89" s="26"/>
+      <c r="Q89" s="26"/>
+      <c r="R89" s="26"/>
       <c r="S89" s="7" t="str">
         <f>IFERROR(VLOOKUP(N89,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6617,35 +6653,35 @@
       </c>
     </row>
     <row r="90" spans="1:26">
-      <c r="A90" s="19">
+      <c r="A90" s="26">
         <v>85</v>
       </c>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="19"/>
-      <c r="G90" s="19"/>
-      <c r="H90" s="19"/>
-      <c r="I90" s="45">
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="26"/>
+      <c r="F90" s="25"/>
+      <c r="G90" s="26"/>
+      <c r="H90" s="26"/>
+      <c r="I90" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J90" s="19"/>
-      <c r="K90" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L90" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M90" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N90" s="19"/>
-      <c r="O90" s="19"/>
-      <c r="P90" s="19"/>
-      <c r="Q90" s="19"/>
-      <c r="R90" s="19"/>
+      <c r="J90" s="26"/>
+      <c r="K90" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L90" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" s="26"/>
+      <c r="O90" s="26"/>
+      <c r="P90" s="26"/>
+      <c r="Q90" s="26"/>
+      <c r="R90" s="26"/>
       <c r="S90" s="7" t="str">
         <f>IFERROR(VLOOKUP(N90,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6680,35 +6716,35 @@
       </c>
     </row>
     <row r="91" spans="1:26">
-      <c r="A91" s="19">
+      <c r="A91" s="26">
         <v>86</v>
       </c>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="19"/>
-      <c r="G91" s="19"/>
-      <c r="H91" s="19"/>
-      <c r="I91" s="45">
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="26"/>
+      <c r="F91" s="25"/>
+      <c r="G91" s="26"/>
+      <c r="H91" s="26"/>
+      <c r="I91" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J91" s="19"/>
-      <c r="K91" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M91" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N91" s="19"/>
-      <c r="O91" s="19"/>
-      <c r="P91" s="19"/>
-      <c r="Q91" s="19"/>
-      <c r="R91" s="19"/>
+      <c r="J91" s="26"/>
+      <c r="K91" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L91" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" s="26"/>
+      <c r="O91" s="26"/>
+      <c r="P91" s="26"/>
+      <c r="Q91" s="26"/>
+      <c r="R91" s="26"/>
       <c r="S91" s="7" t="str">
         <f>IFERROR(VLOOKUP(N91,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6743,35 +6779,35 @@
       </c>
     </row>
     <row r="92" spans="1:26">
-      <c r="A92" s="19">
+      <c r="A92" s="26">
         <v>87</v>
       </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
-      <c r="G92" s="19"/>
-      <c r="H92" s="19"/>
-      <c r="I92" s="45">
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="25"/>
+      <c r="G92" s="26"/>
+      <c r="H92" s="26"/>
+      <c r="I92" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J92" s="19"/>
-      <c r="K92" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L92" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M92" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N92" s="19"/>
-      <c r="O92" s="19"/>
-      <c r="P92" s="19"/>
-      <c r="Q92" s="19"/>
-      <c r="R92" s="19"/>
+      <c r="J92" s="26"/>
+      <c r="K92" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L92" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" s="26"/>
+      <c r="O92" s="26"/>
+      <c r="P92" s="26"/>
+      <c r="Q92" s="26"/>
+      <c r="R92" s="26"/>
       <c r="S92" s="7" t="str">
         <f>IFERROR(VLOOKUP(N92,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6806,35 +6842,35 @@
       </c>
     </row>
     <row r="93" spans="1:26">
-      <c r="A93" s="19">
+      <c r="A93" s="26">
         <v>88</v>
       </c>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="19"/>
-      <c r="G93" s="19"/>
-      <c r="H93" s="19"/>
-      <c r="I93" s="45">
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="25"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="25"/>
+      <c r="G93" s="26"/>
+      <c r="H93" s="26"/>
+      <c r="I93" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J93" s="19"/>
-      <c r="K93" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L93" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M93" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N93" s="19"/>
-      <c r="O93" s="19"/>
-      <c r="P93" s="19"/>
-      <c r="Q93" s="19"/>
-      <c r="R93" s="19"/>
+      <c r="J93" s="26"/>
+      <c r="K93" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L93" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" s="26"/>
+      <c r="O93" s="26"/>
+      <c r="P93" s="26"/>
+      <c r="Q93" s="26"/>
+      <c r="R93" s="26"/>
       <c r="S93" s="7" t="str">
         <f>IFERROR(VLOOKUP(N93,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6869,35 +6905,35 @@
       </c>
     </row>
     <row r="94" spans="1:26">
-      <c r="A94" s="19">
+      <c r="A94" s="26">
         <v>89</v>
       </c>
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="19"/>
-      <c r="G94" s="19"/>
-      <c r="H94" s="19"/>
-      <c r="I94" s="45">
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="26"/>
+      <c r="F94" s="25"/>
+      <c r="G94" s="26"/>
+      <c r="H94" s="26"/>
+      <c r="I94" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J94" s="19"/>
-      <c r="K94" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L94" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M94" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N94" s="19"/>
-      <c r="O94" s="19"/>
-      <c r="P94" s="19"/>
-      <c r="Q94" s="19"/>
-      <c r="R94" s="19"/>
+      <c r="J94" s="26"/>
+      <c r="K94" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L94" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" s="26"/>
+      <c r="O94" s="26"/>
+      <c r="P94" s="26"/>
+      <c r="Q94" s="26"/>
+      <c r="R94" s="26"/>
       <c r="S94" s="7" t="str">
         <f>IFERROR(VLOOKUP(N94,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6932,35 +6968,35 @@
       </c>
     </row>
     <row r="95" spans="1:26">
-      <c r="A95" s="19">
+      <c r="A95" s="26">
         <v>90</v>
       </c>
-      <c r="B95" s="19"/>
-      <c r="C95" s="19"/>
-      <c r="D95" s="19"/>
-      <c r="E95" s="19"/>
-      <c r="F95" s="19"/>
-      <c r="G95" s="19"/>
-      <c r="H95" s="19"/>
-      <c r="I95" s="45">
+      <c r="B95" s="26"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="26"/>
+      <c r="F95" s="25"/>
+      <c r="G95" s="26"/>
+      <c r="H95" s="26"/>
+      <c r="I95" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J95" s="19"/>
-      <c r="K95" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L95" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M95" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N95" s="19"/>
-      <c r="O95" s="19"/>
-      <c r="P95" s="19"/>
-      <c r="Q95" s="19"/>
-      <c r="R95" s="19"/>
+      <c r="J95" s="26"/>
+      <c r="K95" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L95" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" s="26"/>
+      <c r="O95" s="26"/>
+      <c r="P95" s="26"/>
+      <c r="Q95" s="26"/>
+      <c r="R95" s="26"/>
       <c r="S95" s="7" t="str">
         <f>IFERROR(VLOOKUP(N95,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -6995,35 +7031,35 @@
       </c>
     </row>
     <row r="96" spans="1:26">
-      <c r="A96" s="19">
+      <c r="A96" s="26">
         <v>91</v>
       </c>
-      <c r="B96" s="19"/>
-      <c r="C96" s="19"/>
-      <c r="D96" s="19"/>
-      <c r="E96" s="19"/>
-      <c r="F96" s="19"/>
-      <c r="G96" s="19"/>
-      <c r="H96" s="19"/>
-      <c r="I96" s="45">
+      <c r="B96" s="26"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="26"/>
+      <c r="F96" s="25"/>
+      <c r="G96" s="26"/>
+      <c r="H96" s="26"/>
+      <c r="I96" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J96" s="19"/>
-      <c r="K96" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L96" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M96" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N96" s="19"/>
-      <c r="O96" s="19"/>
-      <c r="P96" s="19"/>
-      <c r="Q96" s="19"/>
-      <c r="R96" s="19"/>
+      <c r="J96" s="26"/>
+      <c r="K96" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L96" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" s="26"/>
+      <c r="O96" s="26"/>
+      <c r="P96" s="26"/>
+      <c r="Q96" s="26"/>
+      <c r="R96" s="26"/>
       <c r="S96" s="7" t="str">
         <f>IFERROR(VLOOKUP(N96,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7058,35 +7094,35 @@
       </c>
     </row>
     <row r="97" spans="1:26">
-      <c r="A97" s="19">
+      <c r="A97" s="26">
         <v>92</v>
       </c>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
-      <c r="G97" s="19"/>
-      <c r="H97" s="19"/>
-      <c r="I97" s="45">
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="25"/>
+      <c r="G97" s="26"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J97" s="19"/>
-      <c r="K97" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L97" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M97" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N97" s="19"/>
-      <c r="O97" s="19"/>
-      <c r="P97" s="19"/>
-      <c r="Q97" s="19"/>
-      <c r="R97" s="19"/>
+      <c r="J97" s="26"/>
+      <c r="K97" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L97" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" s="26"/>
+      <c r="O97" s="26"/>
+      <c r="P97" s="26"/>
+      <c r="Q97" s="26"/>
+      <c r="R97" s="26"/>
       <c r="S97" s="7" t="str">
         <f>IFERROR(VLOOKUP(N97,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7121,35 +7157,35 @@
       </c>
     </row>
     <row r="98" spans="1:26">
-      <c r="A98" s="19">
+      <c r="A98" s="26">
         <v>93</v>
       </c>
-      <c r="B98" s="19"/>
-      <c r="C98" s="19"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-      <c r="F98" s="19"/>
-      <c r="G98" s="19"/>
-      <c r="H98" s="19"/>
-      <c r="I98" s="45">
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="26"/>
+      <c r="F98" s="25"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="26"/>
+      <c r="I98" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J98" s="19"/>
-      <c r="K98" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L98" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M98" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N98" s="19"/>
-      <c r="O98" s="19"/>
-      <c r="P98" s="19"/>
-      <c r="Q98" s="19"/>
-      <c r="R98" s="19"/>
+      <c r="J98" s="26"/>
+      <c r="K98" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L98" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" s="26"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="26"/>
+      <c r="Q98" s="26"/>
+      <c r="R98" s="26"/>
       <c r="S98" s="7" t="str">
         <f>IFERROR(VLOOKUP(N98,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7184,35 +7220,35 @@
       </c>
     </row>
     <row r="99" spans="1:26">
-      <c r="A99" s="19">
+      <c r="A99" s="26">
         <v>94</v>
       </c>
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="19"/>
-      <c r="G99" s="19"/>
-      <c r="H99" s="19"/>
-      <c r="I99" s="45">
+      <c r="B99" s="26"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="25"/>
+      <c r="E99" s="26"/>
+      <c r="F99" s="25"/>
+      <c r="G99" s="26"/>
+      <c r="H99" s="26"/>
+      <c r="I99" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J99" s="19"/>
-      <c r="K99" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L99" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M99" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N99" s="19"/>
-      <c r="O99" s="19"/>
-      <c r="P99" s="19"/>
-      <c r="Q99" s="19"/>
-      <c r="R99" s="19"/>
+      <c r="J99" s="26"/>
+      <c r="K99" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L99" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N99" s="26"/>
+      <c r="O99" s="26"/>
+      <c r="P99" s="26"/>
+      <c r="Q99" s="26"/>
+      <c r="R99" s="26"/>
       <c r="S99" s="7" t="str">
         <f>IFERROR(VLOOKUP(N99,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7247,35 +7283,35 @@
       </c>
     </row>
     <row r="100" spans="1:26">
-      <c r="A100" s="19">
+      <c r="A100" s="26">
         <v>95</v>
       </c>
-      <c r="B100" s="19"/>
-      <c r="C100" s="19"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-      <c r="F100" s="19"/>
-      <c r="G100" s="19"/>
-      <c r="H100" s="19"/>
-      <c r="I100" s="45">
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="25"/>
+      <c r="E100" s="26"/>
+      <c r="F100" s="25"/>
+      <c r="G100" s="26"/>
+      <c r="H100" s="26"/>
+      <c r="I100" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J100" s="19"/>
-      <c r="K100" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L100" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M100" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N100" s="19"/>
-      <c r="O100" s="19"/>
-      <c r="P100" s="19"/>
-      <c r="Q100" s="19"/>
-      <c r="R100" s="19"/>
+      <c r="J100" s="26"/>
+      <c r="K100" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L100" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N100" s="26"/>
+      <c r="O100" s="26"/>
+      <c r="P100" s="26"/>
+      <c r="Q100" s="26"/>
+      <c r="R100" s="26"/>
       <c r="S100" s="7" t="str">
         <f>IFERROR(VLOOKUP(N100,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7310,35 +7346,35 @@
       </c>
     </row>
     <row r="101" spans="1:26">
-      <c r="A101" s="19">
+      <c r="A101" s="26">
         <v>96</v>
       </c>
-      <c r="B101" s="19"/>
-      <c r="C101" s="19"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-      <c r="F101" s="19"/>
-      <c r="G101" s="19"/>
-      <c r="H101" s="19"/>
-      <c r="I101" s="45">
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="26"/>
+      <c r="F101" s="25"/>
+      <c r="G101" s="26"/>
+      <c r="H101" s="26"/>
+      <c r="I101" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J101" s="19"/>
-      <c r="K101" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L101" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M101" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N101" s="19"/>
-      <c r="O101" s="19"/>
-      <c r="P101" s="19"/>
-      <c r="Q101" s="19"/>
-      <c r="R101" s="19"/>
+      <c r="J101" s="26"/>
+      <c r="K101" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L101" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N101" s="26"/>
+      <c r="O101" s="26"/>
+      <c r="P101" s="26"/>
+      <c r="Q101" s="26"/>
+      <c r="R101" s="26"/>
       <c r="S101" s="7" t="str">
         <f>IFERROR(VLOOKUP(N101,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7373,35 +7409,35 @@
       </c>
     </row>
     <row r="102" spans="1:26">
-      <c r="A102" s="19">
+      <c r="A102" s="26">
         <v>97</v>
       </c>
-      <c r="B102" s="19"/>
-      <c r="C102" s="19"/>
-      <c r="D102" s="19"/>
-      <c r="E102" s="19"/>
-      <c r="F102" s="19"/>
-      <c r="G102" s="19"/>
-      <c r="H102" s="19"/>
-      <c r="I102" s="45">
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="25"/>
+      <c r="E102" s="26"/>
+      <c r="F102" s="25"/>
+      <c r="G102" s="26"/>
+      <c r="H102" s="26"/>
+      <c r="I102" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J102" s="19"/>
-      <c r="K102" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L102" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M102" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N102" s="19"/>
-      <c r="O102" s="19"/>
-      <c r="P102" s="19"/>
-      <c r="Q102" s="19"/>
-      <c r="R102" s="19"/>
+      <c r="J102" s="26"/>
+      <c r="K102" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L102" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M102" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N102" s="26"/>
+      <c r="O102" s="26"/>
+      <c r="P102" s="26"/>
+      <c r="Q102" s="26"/>
+      <c r="R102" s="26"/>
       <c r="S102" s="7" t="str">
         <f>IFERROR(VLOOKUP(N102,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7436,35 +7472,35 @@
       </c>
     </row>
     <row r="103" spans="1:26">
-      <c r="A103" s="19">
+      <c r="A103" s="26">
         <v>98</v>
       </c>
-      <c r="B103" s="19"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="19"/>
-      <c r="E103" s="19"/>
-      <c r="F103" s="19"/>
-      <c r="G103" s="19"/>
-      <c r="H103" s="19"/>
-      <c r="I103" s="45">
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="25"/>
+      <c r="E103" s="26"/>
+      <c r="F103" s="25"/>
+      <c r="G103" s="26"/>
+      <c r="H103" s="26"/>
+      <c r="I103" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J103" s="19"/>
-      <c r="K103" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L103" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M103" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N103" s="19"/>
-      <c r="O103" s="19"/>
-      <c r="P103" s="19"/>
-      <c r="Q103" s="19"/>
-      <c r="R103" s="19"/>
+      <c r="J103" s="26"/>
+      <c r="K103" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L103" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M103" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N103" s="26"/>
+      <c r="O103" s="26"/>
+      <c r="P103" s="26"/>
+      <c r="Q103" s="26"/>
+      <c r="R103" s="26"/>
       <c r="S103" s="7" t="str">
         <f>IFERROR(VLOOKUP(N103,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7499,35 +7535,35 @@
       </c>
     </row>
     <row r="104" spans="1:26">
-      <c r="A104" s="19">
+      <c r="A104" s="26">
         <v>99</v>
       </c>
-      <c r="B104" s="19"/>
-      <c r="C104" s="19"/>
-      <c r="D104" s="19"/>
-      <c r="E104" s="19"/>
-      <c r="F104" s="19"/>
-      <c r="G104" s="19"/>
-      <c r="H104" s="19"/>
-      <c r="I104" s="45">
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="25"/>
+      <c r="E104" s="26"/>
+      <c r="F104" s="25"/>
+      <c r="G104" s="26"/>
+      <c r="H104" s="26"/>
+      <c r="I104" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J104" s="19"/>
-      <c r="K104" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L104" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M104" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N104" s="19"/>
-      <c r="O104" s="19"/>
-      <c r="P104" s="19"/>
-      <c r="Q104" s="19"/>
-      <c r="R104" s="19"/>
+      <c r="J104" s="26"/>
+      <c r="K104" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L104" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M104" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N104" s="26"/>
+      <c r="O104" s="26"/>
+      <c r="P104" s="26"/>
+      <c r="Q104" s="26"/>
+      <c r="R104" s="26"/>
       <c r="S104" s="7" t="str">
         <f>IFERROR(VLOOKUP(N104,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7562,35 +7598,35 @@
       </c>
     </row>
     <row r="105" spans="1:26">
-      <c r="A105" s="19">
+      <c r="A105" s="26">
         <v>100</v>
       </c>
-      <c r="B105" s="19"/>
-      <c r="C105" s="19"/>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19"/>
-      <c r="F105" s="19"/>
-      <c r="G105" s="19"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="45">
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="25"/>
+      <c r="E105" s="26"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="26"/>
+      <c r="H105" s="26"/>
+      <c r="I105" s="25">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J105" s="19"/>
-      <c r="K105" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L105" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="M105" s="20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N105" s="19"/>
-      <c r="O105" s="19"/>
-      <c r="P105" s="19"/>
-      <c r="Q105" s="19"/>
-      <c r="R105" s="19"/>
+      <c r="J105" s="26"/>
+      <c r="K105" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L105" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="M105" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N105" s="26"/>
+      <c r="O105" s="26"/>
+      <c r="P105" s="26"/>
+      <c r="Q105" s="26"/>
+      <c r="R105" s="26"/>
       <c r="S105" s="7" t="str">
         <f>IFERROR(VLOOKUP(N105,Scoring!$C$7:$E$10,2,FALSE),"")</f>
         <v/>
@@ -7629,15 +7665,18 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E1:R3"/>
     <mergeCell ref="X1:Z3"/>
+    <mergeCell ref="D1:R1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5:E105" xr:uid="{7F845269-5E48-4BC8-9375-F3C0B14EEEC2}">
       <formula1>"RHD,LHD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{24190701-B7DE-4012-A261-5ED2C17AEA1C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F105" xr:uid="{24190701-B7DE-4012-A261-5ED2C17AEA1C}">
       <formula1>"Export,Domestic"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D105" xr:uid="{ACC9C22A-B5E6-4CA0-8071-8590CFAA9E1D}">
+      <formula1>"BIW,Hangeons,Assy Part"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7785,16 +7824,16 @@
       <c r="B8" s="3">
         <v>1</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="26">
         <v>175</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="26">
         <f>D8/D10</f>
         <v>5</v>
       </c>
@@ -7803,16 +7842,16 @@
       <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="26">
         <v>105</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="26">
         <f>D9/D10</f>
         <v>3</v>
       </c>
@@ -7821,16 +7860,16 @@
       <c r="B10" s="3">
         <v>3</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="26">
         <v>35</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="26">
         <f>D10/D10</f>
         <v>1</v>
       </c>
@@ -7856,16 +7895,16 @@
       <c r="B13" s="3">
         <v>1</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="26">
         <v>125</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="26">
         <f>D13/D15</f>
         <v>5</v>
       </c>
@@ -7874,16 +7913,16 @@
       <c r="B14" s="3">
         <v>2</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="26">
         <v>75</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="26" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="26">
         <f>D14/D15</f>
         <v>3</v>
       </c>
@@ -7892,16 +7931,16 @@
       <c r="B15" s="3">
         <v>3</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="26">
         <v>25</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="26" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="26">
         <f>D15/D15</f>
         <v>1</v>
       </c>
@@ -7927,16 +7966,16 @@
       <c r="B18" s="3">
         <v>1</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="26">
         <v>50</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="26">
         <f>D18/D20</f>
         <v>5</v>
       </c>
@@ -7945,16 +7984,16 @@
       <c r="B19" s="3">
         <v>2</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="26">
         <v>30</v>
       </c>
-      <c r="E19" s="19" t="s">
+      <c r="E19" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="26">
         <f>D19/D20</f>
         <v>3</v>
       </c>
@@ -7963,16 +8002,16 @@
       <c r="B20" s="3">
         <v>3</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="26">
         <v>10</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="26">
         <f>D20/D20</f>
         <v>1</v>
       </c>
@@ -7998,16 +8037,16 @@
       <c r="B23" s="3">
         <v>1</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="26">
         <v>100</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="26">
         <f>D23/D25</f>
         <v>5</v>
       </c>
@@ -8016,16 +8055,16 @@
       <c r="B24" s="3">
         <v>2</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="26">
         <v>60</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="26">
         <f>D24/D25</f>
         <v>3</v>
       </c>
@@ -8034,16 +8073,16 @@
       <c r="B25" s="3">
         <v>3</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="26">
         <v>20</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="26">
         <f>D25/D25</f>
         <v>1</v>
       </c>
@@ -8069,16 +8108,16 @@
       <c r="B28" s="3">
         <v>1</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="26">
         <v>50</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="E28" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="26">
         <f>D28/D30</f>
         <v>5</v>
       </c>
@@ -8087,16 +8126,16 @@
       <c r="B29" s="3">
         <v>2</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="26" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="26">
         <v>30</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="G29" s="19">
+      <c r="G29" s="26">
         <f>D29/D30</f>
         <v>3</v>
       </c>
@@ -8105,16 +8144,16 @@
       <c r="B30" s="3">
         <v>3</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="26">
         <v>10</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="26">
         <f>D30/D30</f>
         <v>1</v>
       </c>
